--- a/12624955.xlsx
+++ b/12624955.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9114f0d97d67d985/Desktop/git demo/CAP776/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9114f0d97d67d985/Desktop/Activity/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{921ECD1B-E566-4BD9-AD03-15B8ED5BFBEB}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{873132B9-2A47-4F78-BE3D-6C141A146368}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -263,6 +263,9 @@
   </si>
   <si>
     <t xml:space="preserve">mca  </t>
+  </si>
+  <si>
+    <t>just a casual day.</t>
   </si>
 </sst>
 </file>
@@ -2324,7 +2327,7 @@
         <v>51</v>
       </c>
       <c r="N33" s="17" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">

--- a/12624955.xlsx
+++ b/12624955.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9114f0d97d67d985/Desktop/Activity/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{873132B9-2A47-4F78-BE3D-6C141A146368}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1C9DEB6-C90B-42EF-A265-4A559B7F81FC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -267,6 +267,9 @@
   <si>
     <t>just a casual day.</t>
   </si>
+  <si>
+    <t>I play cricket</t>
+  </si>
 </sst>
 </file>
 
@@ -275,7 +278,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -356,6 +359,12 @@
       <name val="Arial"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -404,7 +413,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -448,11 +457,125 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -916,7 +1039,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N401"/>
+  <dimension ref="A1:N408"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1068,11 +1191,11 @@
         <v>30</v>
       </c>
       <c r="I6" s="10">
-        <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <f t="shared" ref="I6:I76" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>885</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
+        <f t="shared" ref="J6:J76" si="1">IF(I6="","",1440-I6)</f>
         <v>555</v>
       </c>
       <c r="K6" s="11" t="s">
@@ -1090,451 +1213,451 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="13">
-        <v>46260</v>
+        <v>46253</v>
       </c>
       <c r="B7" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="C7" s="14">
         <v>60</v>
       </c>
       <c r="D7" s="14">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="E7" s="14">
         <v>60</v>
       </c>
       <c r="F7" s="14">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G7" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H7" s="14">
         <v>120</v>
       </c>
-      <c r="I7" s="15">
+      <c r="I7" s="22">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
+      <c r="J7" s="22">
+        <f t="shared" si="1"/>
+        <v>440</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B8" s="14">
+        <v>360</v>
+      </c>
+      <c r="C8" s="14">
+        <v>120</v>
+      </c>
+      <c r="D8" s="14">
+        <v>120</v>
+      </c>
+      <c r="E8" s="14">
+        <v>100</v>
+      </c>
+      <c r="F8" s="14">
+        <v>200</v>
+      </c>
+      <c r="G8" s="14">
+        <v>4</v>
+      </c>
+      <c r="H8" s="14">
+        <v>120</v>
+      </c>
+      <c r="I8" s="22">
+        <f t="shared" si="0"/>
+        <v>1020</v>
+      </c>
+      <c r="J8" s="22">
+        <f t="shared" si="1"/>
+        <v>420</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B9" s="14">
+        <v>360</v>
+      </c>
+      <c r="C9" s="14">
+        <v>60</v>
+      </c>
+      <c r="D9" s="14">
+        <v>180</v>
+      </c>
+      <c r="E9" s="14">
+        <v>60</v>
+      </c>
+      <c r="F9" s="14">
+        <v>250</v>
+      </c>
+      <c r="G9" s="14">
+        <v>5</v>
+      </c>
+      <c r="H9" s="14">
+        <v>120</v>
+      </c>
+      <c r="I9" s="22">
+        <f t="shared" si="0"/>
+        <v>1030</v>
+      </c>
+      <c r="J9" s="22">
+        <f t="shared" si="1"/>
+        <v>410</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B10" s="14">
+        <v>420</v>
+      </c>
+      <c r="C10" s="14">
+        <v>120</v>
+      </c>
+      <c r="D10" s="14">
+        <v>180</v>
+      </c>
+      <c r="E10" s="14">
+        <v>50</v>
+      </c>
+      <c r="F10" s="14">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14">
+        <v>120</v>
+      </c>
+      <c r="I10" s="22">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J10" s="22">
+        <f t="shared" si="1"/>
+        <v>550</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B11" s="14">
+        <v>420</v>
+      </c>
+      <c r="C11" s="14">
+        <v>100</v>
+      </c>
+      <c r="D11" s="14">
+        <v>240</v>
+      </c>
+      <c r="E11" s="14">
+        <v>120</v>
+      </c>
+      <c r="F11" s="14">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14">
+        <v>100</v>
+      </c>
+      <c r="I11" s="22">
         <f t="shared" si="0"/>
         <v>980</v>
       </c>
-      <c r="J7" s="15">
+      <c r="J11" s="22">
         <f t="shared" si="1"/>
         <v>460</v>
       </c>
-      <c r="K7" s="16" t="s">
+      <c r="K11" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B12" s="14">
+        <v>360</v>
+      </c>
+      <c r="C12" s="14">
+        <v>60</v>
+      </c>
+      <c r="D12" s="14">
+        <v>200</v>
+      </c>
+      <c r="E12" s="14">
+        <v>120</v>
+      </c>
+      <c r="F12" s="14">
+        <v>200</v>
+      </c>
+      <c r="G12" s="14">
+        <v>4</v>
+      </c>
+      <c r="H12" s="14">
+        <v>120</v>
+      </c>
+      <c r="I12" s="22">
+        <f t="shared" si="0"/>
+        <v>1060</v>
+      </c>
+      <c r="J12" s="22">
+        <f t="shared" si="1"/>
+        <v>380</v>
+      </c>
+      <c r="K12" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="L7" s="16" t="s">
+      <c r="L12" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B13" s="14">
+        <v>360</v>
+      </c>
+      <c r="C13" s="14">
+        <v>60</v>
+      </c>
+      <c r="D13" s="14">
+        <v>180</v>
+      </c>
+      <c r="E13" s="14">
+        <v>60</v>
+      </c>
+      <c r="F13" s="14">
+        <v>180</v>
+      </c>
+      <c r="G13" s="14">
+        <v>3</v>
+      </c>
+      <c r="H13" s="14">
+        <v>120</v>
+      </c>
+      <c r="I13" s="22">
+        <f t="shared" si="0"/>
+        <v>960</v>
+      </c>
+      <c r="J13" s="22">
+        <f t="shared" si="1"/>
+        <v>480</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L13" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M7" s="16" t="s">
+      <c r="M13" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N7" s="17" t="s">
+      <c r="N13" s="17" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B14" s="21">
+        <v>360</v>
+      </c>
+      <c r="C14" s="14">
+        <v>60</v>
+      </c>
+      <c r="D14" s="14">
+        <v>180</v>
+      </c>
+      <c r="E14" s="14">
+        <v>60</v>
+      </c>
+      <c r="F14" s="14">
+        <v>200</v>
+      </c>
+      <c r="G14" s="14">
+        <v>4</v>
+      </c>
+      <c r="H14" s="14">
+        <v>120</v>
+      </c>
+      <c r="I14" s="15">
+        <f t="shared" si="0"/>
+        <v>980</v>
+      </c>
+      <c r="J14" s="15">
+        <f t="shared" si="1"/>
+        <v>460</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="13">
         <v>46261</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B15" s="14">
         <v>300</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C15" s="14">
         <v>60</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D15" s="14">
         <v>180</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E15" s="14">
         <v>80</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F15" s="14">
         <v>240</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G15" s="14">
         <v>5</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H15" s="14">
         <v>140</v>
       </c>
-      <c r="I8" s="15">
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-      <c r="J8" s="15">
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
         <v>440</v>
       </c>
-      <c r="K8" s="16" t="s">
+      <c r="K15" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L8" s="16" t="s">
+      <c r="L15" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M8" s="16" t="s">
+      <c r="M15" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N8" s="17" t="s">
+      <c r="N15" s="17" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="13">
         <v>46262</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B16" s="14">
         <v>340</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C16" s="14">
         <v>60</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D16" s="14">
         <v>220</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E16" s="14">
         <v>60</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F16" s="14">
         <v>320</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G16" s="14">
         <v>6</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H16" s="14">
         <v>100</v>
       </c>
-      <c r="I9" s="15">
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
         <v>1100</v>
       </c>
-      <c r="J9" s="15">
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
         <v>340</v>
       </c>
-      <c r="K9" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="L9" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M9" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N9" s="17" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="13">
-        <v>46263</v>
-      </c>
-      <c r="B10" s="14">
-        <v>300</v>
-      </c>
-      <c r="C10" s="14">
-        <v>0</v>
-      </c>
-      <c r="D10" s="14">
-        <v>240</v>
-      </c>
-      <c r="E10" s="14">
-        <v>100</v>
-      </c>
-      <c r="F10" s="14">
-        <v>180</v>
-      </c>
-      <c r="G10" s="14">
-        <v>3</v>
-      </c>
-      <c r="H10" s="14">
-        <v>140</v>
-      </c>
-      <c r="I10" s="15">
-        <f t="shared" si="0"/>
-        <v>960</v>
-      </c>
-      <c r="J10" s="15">
-        <f t="shared" si="1"/>
-        <v>480</v>
-      </c>
-      <c r="K10" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="L10" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M10" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N10" s="17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13">
-        <v>46264</v>
-      </c>
-      <c r="B11" s="14">
-        <v>420</v>
-      </c>
-      <c r="C11" s="14">
-        <v>100</v>
-      </c>
-      <c r="D11" s="14">
-        <v>330</v>
-      </c>
-      <c r="E11" s="14">
-        <v>50</v>
-      </c>
-      <c r="F11" s="14">
-        <v>0</v>
-      </c>
-      <c r="G11" s="14">
-        <v>0</v>
-      </c>
-      <c r="H11" s="14">
-        <v>200</v>
-      </c>
-      <c r="I11" s="15">
-        <f t="shared" si="0"/>
-        <v>1100</v>
-      </c>
-      <c r="J11" s="15">
-        <f t="shared" si="1"/>
-        <v>340</v>
-      </c>
-      <c r="K11" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="L11" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M11" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="N11" s="17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13">
-        <v>46265</v>
-      </c>
-      <c r="B12" s="14">
-        <v>300</v>
-      </c>
-      <c r="C12" s="14">
-        <v>120</v>
-      </c>
-      <c r="D12" s="14">
-        <v>200</v>
-      </c>
-      <c r="E12" s="14">
-        <v>100</v>
-      </c>
-      <c r="F12" s="14">
-        <v>250</v>
-      </c>
-      <c r="G12" s="14">
-        <v>5</v>
-      </c>
-      <c r="H12" s="14">
-        <v>60</v>
-      </c>
-      <c r="I12" s="15">
-        <f t="shared" si="0"/>
-        <v>1030</v>
-      </c>
-      <c r="J12" s="15">
-        <f t="shared" si="1"/>
-        <v>410</v>
-      </c>
-      <c r="K12" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="L12" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M12" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="N12" s="17" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13">
-        <v>46266</v>
-      </c>
-      <c r="B13" s="14">
-        <v>360</v>
-      </c>
-      <c r="C13" s="14">
-        <v>60</v>
-      </c>
-      <c r="D13" s="14">
-        <v>220</v>
-      </c>
-      <c r="E13" s="14">
-        <v>60</v>
-      </c>
-      <c r="F13" s="14">
-        <v>150</v>
-      </c>
-      <c r="G13" s="14">
-        <v>3</v>
-      </c>
-      <c r="H13" s="14">
-        <v>100</v>
-      </c>
-      <c r="I13" s="15">
-        <f t="shared" si="0"/>
-        <v>950</v>
-      </c>
-      <c r="J13" s="15">
-        <f t="shared" si="1"/>
-        <v>490</v>
-      </c>
-      <c r="K13" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="L13" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="M13" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N13" s="17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13">
-        <v>46267</v>
-      </c>
-      <c r="B14" s="14">
-        <v>360</v>
-      </c>
-      <c r="C14" s="14">
-        <v>60</v>
-      </c>
-      <c r="D14" s="14">
-        <v>180</v>
-      </c>
-      <c r="E14" s="14">
-        <v>50</v>
-      </c>
-      <c r="F14" s="14">
-        <v>400</v>
-      </c>
-      <c r="G14" s="14">
-        <v>8</v>
-      </c>
-      <c r="H14" s="14">
-        <v>40</v>
-      </c>
-      <c r="I14" s="15">
-        <f t="shared" si="0"/>
-        <v>1090</v>
-      </c>
-      <c r="J14" s="15">
-        <f t="shared" si="1"/>
-        <v>350</v>
-      </c>
-      <c r="K14" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="L14" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M14" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="N14" s="17" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13">
-        <v>46268</v>
-      </c>
-      <c r="B15" s="14">
-        <v>360</v>
-      </c>
-      <c r="C15" s="14">
-        <v>60</v>
-      </c>
-      <c r="D15" s="14">
-        <v>240</v>
-      </c>
-      <c r="E15" s="14">
-        <v>100</v>
-      </c>
-      <c r="F15" s="14">
-        <v>250</v>
-      </c>
-      <c r="G15" s="14">
-        <v>5</v>
-      </c>
-      <c r="H15" s="14">
-        <v>120</v>
-      </c>
-      <c r="I15" s="15">
-        <f t="shared" si="0"/>
-        <v>1130</v>
-      </c>
-      <c r="J15" s="15">
-        <f t="shared" si="1"/>
-        <v>310</v>
-      </c>
-      <c r="K15" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="L15" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M15" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N15" s="17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13">
-        <v>46269</v>
-      </c>
-      <c r="B16" s="14">
-        <v>300</v>
-      </c>
-      <c r="C16" s="14">
-        <v>60</v>
-      </c>
-      <c r="D16" s="14">
-        <v>180</v>
-      </c>
-      <c r="E16" s="14">
-        <v>100</v>
-      </c>
-      <c r="F16" s="14">
-        <v>200</v>
-      </c>
-      <c r="G16" s="14">
-        <v>4</v>
-      </c>
-      <c r="H16" s="14">
-        <v>60</v>
-      </c>
-      <c r="I16" s="15">
-        <f t="shared" si="0"/>
-        <v>900</v>
-      </c>
-      <c r="J16" s="15">
-        <f t="shared" si="1"/>
-        <v>540</v>
-      </c>
       <c r="K16" s="16" t="s">
         <v>49</v>
       </c>
@@ -1545,33 +1668,33 @@
         <v>51</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="13">
-        <v>46270</v>
+        <v>46263</v>
       </c>
       <c r="B17" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="C17" s="14">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D17" s="14">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="E17" s="14">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F17" s="14">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G17" s="14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H17" s="14">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="I17" s="15">
         <f t="shared" si="0"/>
@@ -1585,18 +1708,18 @@
         <v>59</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="M17" s="16" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="13">
-        <v>46271</v>
+        <v>46264</v>
       </c>
       <c r="B18" s="14">
         <v>420</v>
@@ -1605,10 +1728,10 @@
         <v>100</v>
       </c>
       <c r="D18" s="14">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="E18" s="14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F18" s="14">
         <v>0</v>
@@ -1617,44 +1740,44 @@
         <v>0</v>
       </c>
       <c r="H18" s="14">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v>1040</v>
+        <v>1100</v>
       </c>
       <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>340</v>
       </c>
       <c r="K18" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="M18" s="16" t="s">
         <v>61</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="13">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B19" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="C19" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="D19" s="14">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="E19" s="14">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="F19" s="14">
         <v>250</v>
@@ -1667,40 +1790,40 @@
       </c>
       <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v>950</v>
+        <v>1030</v>
       </c>
       <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v>490</v>
+        <v>410</v>
       </c>
       <c r="K19" s="16" t="s">
         <v>59</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="M19" s="16" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="13">
-        <v>46273</v>
+        <v>46266</v>
       </c>
       <c r="B20" s="14">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="C20" s="14">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D20" s="14">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="E20" s="14">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F20" s="14">
         <v>150</v>
@@ -1709,32 +1832,32 @@
         <v>3</v>
       </c>
       <c r="H20" s="14">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v>750</v>
+        <v>950</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v>690</v>
+        <v>490</v>
       </c>
       <c r="K20" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="M20" s="16" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="13">
-        <v>46274</v>
+        <v>46267</v>
       </c>
       <c r="B21" s="14">
         <v>360</v>
@@ -1746,7 +1869,7 @@
         <v>180</v>
       </c>
       <c r="E21" s="14">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="F21" s="14">
         <v>400</v>
@@ -1755,32 +1878,32 @@
         <v>8</v>
       </c>
       <c r="H21" s="14">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v>1220</v>
+        <v>1090</v>
       </c>
       <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v>220</v>
+        <v>350</v>
       </c>
       <c r="K21" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M21" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="L21" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="M21" s="16" t="s">
-        <v>51</v>
-      </c>
       <c r="N21" s="17" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="13">
-        <v>46275</v>
+        <v>46268</v>
       </c>
       <c r="B22" s="14">
         <v>360</v>
@@ -1789,47 +1912,47 @@
         <v>60</v>
       </c>
       <c r="D22" s="14">
+        <v>240</v>
+      </c>
+      <c r="E22" s="14">
+        <v>100</v>
+      </c>
+      <c r="F22" s="14">
+        <v>250</v>
+      </c>
+      <c r="G22" s="14">
+        <v>5</v>
+      </c>
+      <c r="H22" s="14">
         <v>120</v>
-      </c>
-      <c r="E22" s="14">
-        <v>45</v>
-      </c>
-      <c r="F22" s="14">
-        <v>200</v>
-      </c>
-      <c r="G22" s="14">
-        <v>4</v>
-      </c>
-      <c r="H22" s="14">
-        <v>0</v>
       </c>
       <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v>785</v>
+        <v>1130</v>
       </c>
       <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v>655</v>
+        <v>310</v>
       </c>
       <c r="K22" s="16" t="s">
         <v>59</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="M22" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13">
-        <v>46276</v>
+        <v>46269</v>
       </c>
       <c r="B23" s="14">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="C23" s="14">
         <v>60</v>
@@ -1838,53 +1961,53 @@
         <v>180</v>
       </c>
       <c r="E23" s="14">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F23" s="14">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="G23" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H23" s="14">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v>1040</v>
+        <v>900</v>
       </c>
       <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>540</v>
       </c>
       <c r="K23" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="M23" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="13">
-        <v>46277</v>
+        <v>46270</v>
       </c>
       <c r="B24" s="14">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="C24" s="14">
         <v>60</v>
       </c>
       <c r="D24" s="14">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="E24" s="14">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F24" s="14">
         <v>0</v>
@@ -1893,44 +2016,44 @@
         <v>0</v>
       </c>
       <c r="H24" s="14">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v>840</v>
+        <v>960</v>
       </c>
       <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v>600</v>
+        <v>480</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="M24" s="16" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="13">
-        <v>46278</v>
+        <v>46271</v>
       </c>
       <c r="B25" s="14">
         <v>420</v>
       </c>
       <c r="C25" s="14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D25" s="14">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="E25" s="14">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F25" s="14">
         <v>0</v>
@@ -1939,32 +2062,32 @@
         <v>0</v>
       </c>
       <c r="H25" s="14">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v>1020</v>
+        <v>1040</v>
       </c>
       <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="K25" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="16" t="s">
         <v>59</v>
-      </c>
-      <c r="L25" s="16" t="s">
-        <v>50</v>
       </c>
       <c r="M25" s="16" t="s">
         <v>61</v>
       </c>
       <c r="N25" s="17" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B26" s="14">
         <v>360</v>
@@ -1976,7 +2099,7 @@
         <v>180</v>
       </c>
       <c r="E26" s="14">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F26" s="14">
         <v>250</v>
@@ -1985,15 +2108,15 @@
         <v>5</v>
       </c>
       <c r="H26" s="14">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v>1010</v>
+        <v>950</v>
       </c>
       <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v>430</v>
+        <v>490</v>
       </c>
       <c r="K26" s="16" t="s">
         <v>59</v>
@@ -2005,24 +2128,24 @@
         <v>51</v>
       </c>
       <c r="N26" s="17" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="13">
-        <v>46280</v>
+        <v>46273</v>
       </c>
       <c r="B27" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="C27" s="14">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D27" s="14">
         <v>200</v>
       </c>
       <c r="E27" s="14">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F27" s="14">
         <v>150</v>
@@ -2035,20 +2158,20 @@
       </c>
       <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v>880</v>
+        <v>750</v>
       </c>
       <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v>560</v>
+        <v>690</v>
       </c>
       <c r="K27" s="16" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="L27" s="16" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="M27" s="16" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="N27" s="17" t="s">
         <v>62</v>
@@ -2056,10 +2179,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="13">
-        <v>46281</v>
+        <v>46274</v>
       </c>
       <c r="B28" s="14">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="C28" s="14">
         <v>60</v>
@@ -2068,7 +2191,7 @@
         <v>180</v>
       </c>
       <c r="E28" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F28" s="14">
         <v>400</v>
@@ -2077,32 +2200,32 @@
         <v>8</v>
       </c>
       <c r="H28" s="14">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v>1060</v>
+        <v>1220</v>
       </c>
       <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v>380</v>
+        <v>220</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="L28" s="16" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="M28" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="13">
-        <v>46282</v>
+        <v>46275</v>
       </c>
       <c r="B29" s="14">
         <v>360</v>
@@ -2123,44 +2246,44 @@
         <v>4</v>
       </c>
       <c r="H29" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v>885</v>
+        <v>785</v>
       </c>
       <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v>555</v>
+        <v>655</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="L29" s="16" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="M29" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N29" s="17" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="13">
-        <v>46283</v>
+        <v>46276</v>
       </c>
       <c r="B30" s="14">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="C30" s="14">
         <v>60</v>
       </c>
       <c r="D30" s="14">
+        <v>180</v>
+      </c>
+      <c r="E30" s="14">
         <v>90</v>
-      </c>
-      <c r="E30" s="14">
-        <v>0</v>
       </c>
       <c r="F30" s="14">
         <v>250</v>
@@ -2169,38 +2292,38 @@
         <v>5</v>
       </c>
       <c r="H30" s="14">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v>880</v>
+        <v>1040</v>
       </c>
       <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v>560</v>
+        <v>400</v>
       </c>
       <c r="K30" s="16" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="L30" s="16" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="M30" s="16" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="13">
-        <v>46284</v>
+        <v>46277</v>
       </c>
       <c r="B31" s="14">
-        <v>420</v>
+        <v>300</v>
       </c>
       <c r="C31" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="D31" s="14">
         <v>240</v>
@@ -2215,44 +2338,44 @@
         <v>0</v>
       </c>
       <c r="H31" s="14">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v>930</v>
+        <v>840</v>
       </c>
       <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v>510</v>
+        <v>600</v>
       </c>
       <c r="K31" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L31" s="16" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="M31" s="16" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="N31" s="17" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="13">
-        <v>46285</v>
+        <v>46278</v>
       </c>
       <c r="B32" s="14">
         <v>420</v>
       </c>
       <c r="C32" s="14">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="D32" s="14">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="E32" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="F32" s="14">
         <v>0</v>
@@ -2261,32 +2384,32 @@
         <v>0</v>
       </c>
       <c r="H32" s="14">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v>1050</v>
+        <v>1020</v>
       </c>
       <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v>390</v>
+        <v>420</v>
       </c>
       <c r="K32" s="16" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="L32" s="16" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="M32" s="16" t="s">
         <v>61</v>
       </c>
       <c r="N32" s="17" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="13">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="B33" s="14">
         <v>360</v>
@@ -2295,7 +2418,7 @@
         <v>60</v>
       </c>
       <c r="D33" s="14">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="E33" s="14">
         <v>60</v>
@@ -2307,182 +2430,350 @@
         <v>5</v>
       </c>
       <c r="H33" s="14">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v>940</v>
+        <v>1010</v>
       </c>
       <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v>500</v>
+        <v>430</v>
       </c>
       <c r="K33" s="16" t="s">
         <v>59</v>
       </c>
       <c r="L33" s="16" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="M33" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N33" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A34" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B34" s="14">
+        <v>360</v>
+      </c>
+      <c r="C34" s="14">
+        <v>60</v>
+      </c>
+      <c r="D34" s="14">
+        <v>200</v>
+      </c>
+      <c r="E34" s="14">
+        <v>50</v>
+      </c>
+      <c r="F34" s="14">
+        <v>150</v>
+      </c>
+      <c r="G34" s="14">
+        <v>3</v>
+      </c>
+      <c r="H34" s="14">
+        <v>60</v>
+      </c>
+      <c r="I34" s="15">
+        <f t="shared" si="0"/>
+        <v>880</v>
+      </c>
+      <c r="J34" s="15">
+        <f t="shared" si="1"/>
+        <v>560</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A35" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B35" s="14">
+        <v>300</v>
+      </c>
+      <c r="C35" s="14">
+        <v>60</v>
+      </c>
+      <c r="D35" s="14">
+        <v>180</v>
+      </c>
+      <c r="E35" s="14">
+        <v>60</v>
+      </c>
+      <c r="F35" s="14">
+        <v>400</v>
+      </c>
+      <c r="G35" s="14">
+        <v>8</v>
+      </c>
+      <c r="H35" s="14">
+        <v>60</v>
+      </c>
+      <c r="I35" s="15">
+        <f t="shared" si="0"/>
+        <v>1060</v>
+      </c>
+      <c r="J35" s="15">
+        <f t="shared" si="1"/>
+        <v>380</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A36" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B36" s="14">
+        <v>360</v>
+      </c>
+      <c r="C36" s="14">
+        <v>60</v>
+      </c>
+      <c r="D36" s="14">
+        <v>120</v>
+      </c>
+      <c r="E36" s="14">
+        <v>45</v>
+      </c>
+      <c r="F36" s="14">
+        <v>200</v>
+      </c>
+      <c r="G36" s="14">
+        <v>4</v>
+      </c>
+      <c r="H36" s="14">
+        <v>100</v>
+      </c>
+      <c r="I36" s="15">
+        <f t="shared" si="0"/>
+        <v>885</v>
+      </c>
+      <c r="J36" s="15">
+        <f t="shared" si="1"/>
+        <v>555</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B37" s="14">
+        <v>300</v>
+      </c>
+      <c r="C37" s="14">
+        <v>60</v>
+      </c>
+      <c r="D37" s="14">
+        <v>90</v>
+      </c>
+      <c r="E37" s="14">
+        <v>0</v>
+      </c>
+      <c r="F37" s="14">
+        <v>250</v>
+      </c>
+      <c r="G37" s="14">
+        <v>5</v>
+      </c>
+      <c r="H37" s="14">
+        <v>180</v>
+      </c>
+      <c r="I37" s="15">
+        <f t="shared" si="0"/>
+        <v>880</v>
+      </c>
+      <c r="J37" s="15">
+        <f t="shared" si="1"/>
+        <v>560</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A38" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B38" s="14">
+        <v>420</v>
+      </c>
+      <c r="C38" s="14">
+        <v>120</v>
+      </c>
+      <c r="D38" s="14">
+        <v>240</v>
+      </c>
+      <c r="E38" s="14">
+        <v>100</v>
+      </c>
+      <c r="F38" s="14">
+        <v>0</v>
+      </c>
+      <c r="G38" s="14">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14">
+        <v>50</v>
+      </c>
+      <c r="I38" s="15">
+        <f t="shared" si="0"/>
+        <v>930</v>
+      </c>
+      <c r="J38" s="15">
+        <f t="shared" si="1"/>
+        <v>510</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A39" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B39" s="14">
+        <v>420</v>
+      </c>
+      <c r="C39" s="14">
+        <v>150</v>
+      </c>
+      <c r="D39" s="14">
+        <v>300</v>
+      </c>
+      <c r="E39" s="14">
+        <v>120</v>
+      </c>
+      <c r="F39" s="14">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
+        <v>60</v>
+      </c>
+      <c r="I39" s="15">
+        <f t="shared" si="0"/>
+        <v>1050</v>
+      </c>
+      <c r="J39" s="15">
+        <f t="shared" si="1"/>
+        <v>390</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A40" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B40" s="14">
+        <v>360</v>
+      </c>
+      <c r="C40" s="14">
+        <v>60</v>
+      </c>
+      <c r="D40" s="14">
+        <v>120</v>
+      </c>
+      <c r="E40" s="14">
+        <v>60</v>
+      </c>
+      <c r="F40" s="14">
+        <v>250</v>
+      </c>
+      <c r="G40" s="14">
+        <v>5</v>
+      </c>
+      <c r="H40" s="14">
+        <v>90</v>
+      </c>
+      <c r="I40" s="15">
+        <f t="shared" si="0"/>
+        <v>940</v>
+      </c>
+      <c r="J40" s="15">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N40" s="17" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="13"/>
@@ -3132,11 +3423,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3154,11 +3445,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -3176,11 +3467,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -3198,11 +3489,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -3220,11 +3511,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -3242,11 +3533,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -3264,11 +3555,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -3286,11 +3577,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I77:I140" si="2">IF(SUM(B77:F77,H77)=0,"",SUM(B77:F77,H77))</f>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J77:J140" si="3">IF(I77="","",1440-I77)</f>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -4540,11 +4831,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4562,11 +4853,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4584,11 +4875,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4606,11 +4897,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4628,11 +4919,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4650,11 +4941,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4672,11 +4963,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4694,11 +4985,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I141:I204" si="4">IF(SUM(B141:F141,H141)=0,"",SUM(B141:F141,H141))</f>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J141:J204" si="5">IF(I141="","",1440-I141)</f>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -5948,11 +6239,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5970,11 +6261,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5992,11 +6283,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -6014,11 +6305,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -6036,11 +6327,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -6058,11 +6349,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -6080,11 +6371,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -6102,11 +6393,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I205:I268" si="6">IF(SUM(B205:F205,H205)=0,"",SUM(B205:F205,H205))</f>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J205:J268" si="7">IF(I205="","",1440-I205)</f>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -7356,11 +7647,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7378,11 +7669,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7400,11 +7691,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7422,11 +7713,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7444,11 +7735,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7466,11 +7757,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7488,11 +7779,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7510,11 +7801,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I269:I332" si="8">IF(SUM(B269:F269,H269)=0,"",SUM(B269:F269,H269))</f>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J269:J332" si="9">IF(I269="","",1440-I269)</f>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -8764,11 +9055,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8786,11 +9077,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8808,11 +9099,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8830,11 +9121,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8852,11 +9143,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8874,11 +9165,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8896,11 +9187,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8918,11 +9209,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I333:I396" si="10">IF(SUM(B333:F333,H333)=0,"",SUM(B333:F333,H333))</f>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J333:J396" si="11">IF(I333="","",1440-I333)</f>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -10172,11 +10463,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10194,11 +10485,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -10216,11 +10507,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -10238,11 +10529,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -10260,11 +10551,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -10282,11 +10573,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -10304,11 +10595,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -10326,11 +10617,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="I397:I408" si="12">IF(SUM(B397:F397,H397)=0,"",SUM(B397:F397,H397))</f>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="J397:J408" si="13">IF(I397="","",1440-I397)</f>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -10426,6 +10717,160 @@
       <c r="M401" s="16"/>
       <c r="N401" s="17"/>
     </row>
+    <row r="402" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A402" s="13"/>
+      <c r="B402" s="14"/>
+      <c r="C402" s="14"/>
+      <c r="D402" s="14"/>
+      <c r="E402" s="14"/>
+      <c r="F402" s="14"/>
+      <c r="G402" s="14"/>
+      <c r="H402" s="14"/>
+      <c r="I402" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J402" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K402" s="16"/>
+      <c r="L402" s="16"/>
+      <c r="M402" s="16"/>
+      <c r="N402" s="17"/>
+    </row>
+    <row r="403" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A403" s="13"/>
+      <c r="B403" s="14"/>
+      <c r="C403" s="14"/>
+      <c r="D403" s="14"/>
+      <c r="E403" s="14"/>
+      <c r="F403" s="14"/>
+      <c r="G403" s="14"/>
+      <c r="H403" s="14"/>
+      <c r="I403" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J403" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K403" s="16"/>
+      <c r="L403" s="16"/>
+      <c r="M403" s="16"/>
+      <c r="N403" s="17"/>
+    </row>
+    <row r="404" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A404" s="13"/>
+      <c r="B404" s="14"/>
+      <c r="C404" s="14"/>
+      <c r="D404" s="14"/>
+      <c r="E404" s="14"/>
+      <c r="F404" s="14"/>
+      <c r="G404" s="14"/>
+      <c r="H404" s="14"/>
+      <c r="I404" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J404" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K404" s="16"/>
+      <c r="L404" s="16"/>
+      <c r="M404" s="16"/>
+      <c r="N404" s="17"/>
+    </row>
+    <row r="405" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A405" s="13"/>
+      <c r="B405" s="14"/>
+      <c r="C405" s="14"/>
+      <c r="D405" s="14"/>
+      <c r="E405" s="14"/>
+      <c r="F405" s="14"/>
+      <c r="G405" s="14"/>
+      <c r="H405" s="14"/>
+      <c r="I405" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J405" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K405" s="16"/>
+      <c r="L405" s="16"/>
+      <c r="M405" s="16"/>
+      <c r="N405" s="17"/>
+    </row>
+    <row r="406" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A406" s="13"/>
+      <c r="B406" s="14"/>
+      <c r="C406" s="14"/>
+      <c r="D406" s="14"/>
+      <c r="E406" s="14"/>
+      <c r="F406" s="14"/>
+      <c r="G406" s="14"/>
+      <c r="H406" s="14"/>
+      <c r="I406" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J406" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K406" s="16"/>
+      <c r="L406" s="16"/>
+      <c r="M406" s="16"/>
+      <c r="N406" s="17"/>
+    </row>
+    <row r="407" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A407" s="13"/>
+      <c r="B407" s="14"/>
+      <c r="C407" s="14"/>
+      <c r="D407" s="14"/>
+      <c r="E407" s="14"/>
+      <c r="F407" s="14"/>
+      <c r="G407" s="14"/>
+      <c r="H407" s="14"/>
+      <c r="I407" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J407" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K407" s="16"/>
+      <c r="L407" s="16"/>
+      <c r="M407" s="16"/>
+      <c r="N407" s="17"/>
+    </row>
+    <row r="408" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A408" s="13"/>
+      <c r="B408" s="14"/>
+      <c r="C408" s="14"/>
+      <c r="D408" s="14"/>
+      <c r="E408" s="14"/>
+      <c r="F408" s="14"/>
+      <c r="G408" s="14"/>
+      <c r="H408" s="14"/>
+      <c r="I408" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J408" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K408" s="16"/>
+      <c r="L408" s="16"/>
+      <c r="M408" s="16"/>
+      <c r="N408" s="17"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:N4"/>
@@ -10435,21 +10880,56 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J401">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+  <conditionalFormatting sqref="J6 J14:J408">
+    <cfRule type="cellIs" dxfId="9" priority="9" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J8">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J9">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J10">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J11">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J12">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J13">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K408" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L408" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M408" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>
